--- a/filer/13613575_louis.xlsx
+++ b/filer/13613575_louis.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision · Regnskabsår 1/3–28/2 (forskudt)</t>
         </is>
       </c>
     </row>

--- a/filer/13613575_louis.xlsx
+++ b/filer/13613575_louis.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_13613575" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_13613575" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_13613575" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_13613575" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -648,7 +649,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision · Regnskabsår 1/3–28/2 (forskudt)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Den uafhængige revisors erklær · Regnskabsår 1/3–28/2 (forskudt)</t>
         </is>
       </c>
     </row>
@@ -662,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2021=100)</t>
+          <t>Indekstal (2022=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1531,35 +1532,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -3009,35 +3010,35 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
@@ -4391,19 +4392,19 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
@@ -4509,19 +4510,19 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
@@ -4818,6 +4819,148 @@
       </c>
       <c r="F99" s="13">
         <f>IFERROR($F$36/($F$61+$F$68)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B102" s="17">
+        <f>'pengestrom_raw_13613575'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C102" s="17">
+        <f>'pengestrom_raw_13613575'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D102" s="17">
+        <f>'pengestrom_raw_13613575'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E102" s="17">
+        <f>'pengestrom_raw_13613575'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F102" s="17">
+        <f>'pengestrom_raw_13613575'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B103" s="17">
+        <f>'pengestrom_raw_13613575'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C103" s="17">
+        <f>'pengestrom_raw_13613575'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D103" s="17">
+        <f>'pengestrom_raw_13613575'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E103" s="17">
+        <f>'pengestrom_raw_13613575'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F103" s="17">
+        <f>'pengestrom_raw_13613575'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B104" s="17">
+        <f>'pengestrom_raw_13613575'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C104" s="17">
+        <f>'pengestrom_raw_13613575'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D104" s="17">
+        <f>'pengestrom_raw_13613575'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E104" s="17">
+        <f>'pengestrom_raw_13613575'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F104" s="17">
+        <f>'pengestrom_raw_13613575'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B105" s="17">
+        <f>'pengestrom_raw_13613575'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C105" s="17">
+        <f>'pengestrom_raw_13613575'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D105" s="17">
+        <f>'pengestrom_raw_13613575'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E105" s="17">
+        <f>'pengestrom_raw_13613575'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F105" s="17">
+        <f>'pengestrom_raw_13613575'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B106">
+        <f>IF(ABS(('pengestrom_raw_13613575'!$B$2+'pengestrom_raw_13613575'!$B$3+'pengestrom_raw_13613575'!$B$4)-'pengestrom_raw_13613575'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_13613575'!$B$2+'pengestrom_raw_13613575'!$B$3+'pengestrom_raw_13613575'!$B$4)-'pengestrom_raw_13613575'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C106">
+        <f>IF(ABS(('pengestrom_raw_13613575'!$C$2+'pengestrom_raw_13613575'!$C$3+'pengestrom_raw_13613575'!$C$4)-'pengestrom_raw_13613575'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_13613575'!$C$2+'pengestrom_raw_13613575'!$C$3+'pengestrom_raw_13613575'!$C$4)-'pengestrom_raw_13613575'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D106">
+        <f>IF(ABS(('pengestrom_raw_13613575'!$D$2+'pengestrom_raw_13613575'!$D$3+'pengestrom_raw_13613575'!$D$4)-'pengestrom_raw_13613575'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_13613575'!$D$2+'pengestrom_raw_13613575'!$D$3+'pengestrom_raw_13613575'!$D$4)-'pengestrom_raw_13613575'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E106">
+        <f>IF(ABS(('pengestrom_raw_13613575'!$E$2+'pengestrom_raw_13613575'!$E$3+'pengestrom_raw_13613575'!$E$4)-'pengestrom_raw_13613575'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_13613575'!$E$2+'pengestrom_raw_13613575'!$E$3+'pengestrom_raw_13613575'!$E$4)-'pengestrom_raw_13613575'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F106">
+        <f>IF(ABS(('pengestrom_raw_13613575'!$F$2+'pengestrom_raw_13613575'!$F$3+'pengestrom_raw_13613575'!$F$4)-'pengestrom_raw_13613575'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_13613575'!$F$2+'pengestrom_raw_13613575'!$F$3+'pengestrom_raw_13613575'!$F$4)-'pengestrom_raw_13613575'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4850,401 +4993,397 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>1050415</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>1317404</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>1289938</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>1312519</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>1423</v>
       </c>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>221553</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>272159</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>292974</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>324431</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>355</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>369144</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>357464</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>437219</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>441374</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>452422</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>487</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>521381</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>316307</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>432260</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>430792</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>424923</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>462</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>483353</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>598197</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>720084</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>710746</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>759605</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>828</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>842722</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>420135</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>484857</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>532488</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>572424</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>620</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>645075</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>36166</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>37663</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>45376</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>50242</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>50</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>39832</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
+        <v>1133</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>861</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>1623</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Resultat af primær drift</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>196431</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>132021</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>135316</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>158</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>156532</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Indtægter af kapitalandele, dattervirksomheder</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>-9527</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>-13276</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>-12132</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Finansielle indtægter</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>721</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>3656</v>
+      </c>
+      <c r="E13" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="C10" s="16" t="n">
-        <v>1133</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>861</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>1623</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>Resultat af primær drift</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>141884</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>196431</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>132021</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>135316</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Indtægter af kapitalandele, dattervirksomheder</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>-10592</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>-9527</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>-13276</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>-12132</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Finansielle indtægter</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>47</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>41</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>721</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>3656</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>12</v>
+      <c r="F13" s="17" t="n">
+        <v>7949</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>1909</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>1550</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>789</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>271</v>
       </c>
-      <c r="F14" s="16" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>140213</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>195000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>131999</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>141860</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>170</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>165358</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>34374</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>46084</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>32011</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>34197</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>39</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>36229</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>105839</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>148916</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>99988</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>107663</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>27</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>129129</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>854</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>920</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>983</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>989</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>1025</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>1041</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5275,1107 +5414,1107 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>53810</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>39183</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>24556</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>9928</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>53874</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>39183</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>24556</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>9928</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>8830</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>7842</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>7650</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>8297</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>8</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>6979</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>16347</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>27432</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>35999</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>54576</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>62</v>
       </c>
+      <c r="F8" s="17" t="n">
+        <v>55993</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>31491</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>53191</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>68521</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>65927</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>51</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>37698</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>5850</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>3070</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>6315</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>2200</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>2</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>62518</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>91535</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>118485</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>131000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>123</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>100670</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>62715</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>46834</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>30604</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>16828</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F12" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>19138</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>17860</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>19481</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>24483</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>19138</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>17860</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>19481</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>24483</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>26</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>24710</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>135530</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>148578</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>162522</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>165411</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>149</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>125399</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>19501</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>20397</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>17620</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>19449</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>20</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>19723</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>19501</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>20397</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>17620</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>19449</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>20</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>19723</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>9239</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>11962</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>14272</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>15452</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>14</v>
       </c>
+      <c r="F20" s="17" t="n">
+        <v>14602</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
-        <v>178703</v>
-      </c>
-      <c r="C21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>252480</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>225676</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>247454</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>434</v>
       </c>
+      <c r="F21" s="17" t="n">
+        <v>432059</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
-        <v>64617</v>
-      </c>
-      <c r="C22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>5235</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>7424</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>5974</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>8</v>
       </c>
+      <c r="F22" s="17" t="n">
+        <v>10137</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>31789</v>
-      </c>
-      <c r="C23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>34371</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>41126</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>44779</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>47</v>
       </c>
+      <c r="F23" s="17" t="n">
+        <v>56713</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
-        <v>546</v>
-      </c>
-      <c r="C24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>1299</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>1426</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>579</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F24" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
-        <v>2244</v>
-      </c>
-      <c r="C25" s="16" t="n">
+      <c r="B25" s="17" t="n">
         <v>1413</v>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>3116</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="D25" s="17" t="n">
         <v>967</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F25" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>2625</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>2160</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F26" s="17" t="n">
+        <v>2962</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
-        <v>284348</v>
-      </c>
-      <c r="C27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>306673</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>288498</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>315819</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>503</v>
       </c>
+      <c r="F27" s="17" t="n">
+        <v>516473</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
-        <v>225650</v>
-      </c>
-      <c r="C29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>166759</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>132672</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>128310</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>156</v>
       </c>
+      <c r="F29" s="17" t="n">
+        <v>146408</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
-        <v>529499</v>
-      </c>
-      <c r="C30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>493829</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>438790</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>463578</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>829</v>
       </c>
+      <c r="F30" s="17" t="n">
+        <v>682604</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
-        <v>665029</v>
-      </c>
-      <c r="C31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>642407</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>601312</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>628989</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>829</v>
       </c>
+      <c r="F31" s="17" t="n">
+        <v>808003</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>20100</v>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>20100</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>20100</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="F32" s="17" t="n">
         <v>20100</v>
       </c>
-      <c r="F32" s="16" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
-        <v>297299</v>
-      </c>
-      <c r="C37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>303160</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>315583</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>325965</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>355</v>
       </c>
+      <c r="F37" s="17" t="n">
+        <v>387555</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
-        <v>411193</v>
-      </c>
-      <c r="C38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>414655</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>413636</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>423740</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="E38" s="17" t="n">
         <v>467</v>
       </c>
+      <c r="F38" s="17" t="n">
+        <v>493175</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
-        <v>1733</v>
-      </c>
-      <c r="C39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>2412</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>2952</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>4264</v>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="E39" s="17" t="n">
         <v>4</v>
       </c>
+      <c r="F39" s="17" t="n">
+        <v>5242</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
-        <v>1733</v>
-      </c>
-      <c r="C40" s="16" t="n">
+      <c r="B40" s="17" t="n">
         <v>2412</v>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="C40" s="17" t="n">
         <v>2952</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <v>4264</v>
       </c>
-      <c r="F40" s="16" t="n">
+      <c r="E40" s="17" t="n">
         <v>4</v>
       </c>
+      <c r="F40" s="17" t="n">
+        <v>5242</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
-        <v>17225</v>
-      </c>
-      <c r="C44" s="16" t="n">
+      <c r="B44" s="17" t="n">
         <v>442</v>
       </c>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
-        <v>17225</v>
-      </c>
-      <c r="C45" s="16" t="n">
+      <c r="B45" s="17" t="n">
         <v>4248</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="C45" s="17" t="n">
         <v>4212</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>4383</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="E45" s="17" t="n">
         <v>2</v>
       </c>
+      <c r="F45" s="17" t="n">
+        <v>1271</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="17" t="n"/>
+      <c r="F47" s="17" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
-        <v>40203</v>
-      </c>
-      <c r="C50" s="16" t="n">
+      <c r="B50" s="17" t="n">
         <v>47751</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>43413</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>43107</v>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>46</v>
       </c>
+      <c r="F50" s="17" t="n">
+        <v>44569</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
-        <v>242</v>
-      </c>
-      <c r="C51" s="16" t="n">
+      <c r="B51" s="17" t="n">
         <v>36354</v>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="C51" s="17" t="n">
         <v>957</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="D51" s="17" t="n">
         <v>1638</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="E51" s="17" t="n">
         <v>138</v>
       </c>
+      <c r="F51" s="17" t="n">
+        <v>98369</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="n"/>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="17" t="n"/>
+      <c r="E52" s="17" t="n"/>
+      <c r="F52" s="17" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
-        <v>2467</v>
-      </c>
-      <c r="C53" s="16" t="n">
+      <c r="B53" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="C53" s="17" t="n">
         <v>1821</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="D53" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="E53" s="17" t="n">
         <v>3</v>
       </c>
+      <c r="F53" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n">
-        <v>679</v>
-      </c>
-      <c r="C54" s="16" t="n">
+      <c r="B54" s="17" t="n">
         <v>3382</v>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="C54" s="17" t="n">
         <v>1340</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="D54" s="17" t="n">
         <v>2673</v>
       </c>
-      <c r="F54" s="16" t="n">
+      <c r="E54" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F54" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
-        <v>153633</v>
-      </c>
-      <c r="C55" s="16" t="n">
+      <c r="B55" s="17" t="n">
         <v>100585</v>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="C55" s="17" t="n">
         <v>105832</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>114772</v>
       </c>
-      <c r="F55" s="16" t="n">
+      <c r="E55" s="17" t="n">
         <v>129</v>
       </c>
+      <c r="F55" s="17" t="n">
+        <v>123061</v>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="15" t="inlineStr">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B56" s="16" t="n">
-        <v>38333</v>
-      </c>
-      <c r="C56" s="16" t="n">
+      <c r="B56" s="17" t="n">
         <v>36402</v>
       </c>
-      <c r="D56" s="16" t="n">
+      <c r="C56" s="17" t="n">
         <v>28489</v>
       </c>
-      <c r="E56" s="16" t="n">
+      <c r="D56" s="17" t="n">
         <v>37085</v>
       </c>
-      <c r="F56" s="16" t="n">
+      <c r="E56" s="17" t="n">
         <v>39</v>
       </c>
+      <c r="F56" s="17" t="n">
+        <v>42316</v>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="inlineStr">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B57" s="16" t="n">
-        <v>234878</v>
-      </c>
-      <c r="C57" s="16" t="n">
+      <c r="B57" s="17" t="n">
         <v>221092</v>
       </c>
-      <c r="D57" s="16" t="n">
+      <c r="C57" s="17" t="n">
         <v>180512</v>
       </c>
-      <c r="E57" s="16" t="n">
+      <c r="D57" s="17" t="n">
         <v>196602</v>
       </c>
-      <c r="F57" s="16" t="n">
+      <c r="E57" s="17" t="n">
         <v>354</v>
       </c>
+      <c r="F57" s="17" t="n">
+        <v>308315</v>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="17" t="inlineStr">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B58" s="16" t="n">
-        <v>252103</v>
-      </c>
-      <c r="C58" s="16" t="n">
+      <c r="B58" s="17" t="n">
         <v>225340</v>
       </c>
-      <c r="D58" s="16" t="n">
+      <c r="C58" s="17" t="n">
         <v>184724</v>
       </c>
-      <c r="E58" s="16" t="n">
+      <c r="D58" s="17" t="n">
         <v>200985</v>
       </c>
-      <c r="F58" s="16" t="n">
+      <c r="E58" s="17" t="n">
         <v>357</v>
       </c>
+      <c r="F58" s="17" t="n">
+        <v>309586</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="inlineStr">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B59" s="16" t="n">
-        <v>665029</v>
-      </c>
-      <c r="C59" s="16" t="n">
+      <c r="B59" s="17" t="n">
         <v>642407</v>
       </c>
-      <c r="D59" s="16" t="n">
+      <c r="C59" s="17" t="n">
         <v>601312</v>
       </c>
-      <c r="E59" s="16" t="n">
+      <c r="D59" s="17" t="n">
         <v>628989</v>
       </c>
-      <c r="F59" s="16" t="n">
+      <c r="E59" s="17" t="n">
         <v>829</v>
+      </c>
+      <c r="F59" s="17" t="n">
+        <v>808003</v>
       </c>
     </row>
   </sheetData>
@@ -6384,6 +6523,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>201882</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>151703</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>182490</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>183</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>152273</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-53543</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-55334</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-59748</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-32</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-13085</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-156733</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-103431</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-90238</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-88</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-107942</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6414,13 +6675,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2025</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2024</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2023</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -7134,7 +7395,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2023=100)</t>
+          <t>Indekstal for indtjeningsevne (2024=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -7252,7 +7513,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2024=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7428,7 +7689,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2024-2026. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -7606,7 +7867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7651,27 +7912,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2025 t.kr.</t>
+          <t>2026 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7697,19 +7958,19 @@
         </is>
       </c>
       <c r="D3" s="35" t="n">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="E3" s="35" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="F3" s="35" t="n">
-        <v>46</v>
+        <v>331</v>
       </c>
       <c r="G3" s="35" t="n">
-        <v>331</v>
+        <v>0</v>
       </c>
       <c r="H3" s="35" t="n">
-        <v>0</v>
+        <v>1127</v>
       </c>
       <c r="I3" s="36" t="inlineStr">
         <is>
@@ -7734,15 +7995,17 @@
         </is>
       </c>
       <c r="D4" s="38" t="n"/>
-      <c r="E4" s="38" t="n"/>
+      <c r="E4" s="38" t="n">
+        <v>3737</v>
+      </c>
       <c r="F4" s="38" t="n">
-        <v>3737</v>
+        <v>8031</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>8031</v>
+        <v>-2</v>
       </c>
       <c r="H4" s="38" t="n">
-        <v>-2</v>
+        <v>-2503</v>
       </c>
       <c r="I4" s="39" t="inlineStr">
         <is>
@@ -7766,18 +8029,20 @@
           <t>fsa:LongtermDeferredIncome</t>
         </is>
       </c>
-      <c r="D5" s="35" t="n"/>
+      <c r="D5" s="35" t="n">
+        <v>3806</v>
+      </c>
       <c r="E5" s="35" t="n">
-        <v>3806</v>
+        <v>4212</v>
       </c>
       <c r="F5" s="35" t="n">
-        <v>4212</v>
+        <v>4383</v>
       </c>
       <c r="G5" s="35" t="n">
-        <v>4383</v>
+        <v>2</v>
       </c>
       <c r="H5" s="35" t="n">
-        <v>2</v>
+        <v>1271</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -7804,7 +8069,9 @@
       <c r="D6" s="38" t="n"/>
       <c r="E6" s="38" t="n"/>
       <c r="F6" s="38" t="n"/>
-      <c r="G6" s="38" t="n"/>
+      <c r="G6" s="38" t="n">
+        <v>0</v>
+      </c>
       <c r="H6" s="38" t="n">
         <v>0</v>
       </c>
@@ -7833,7 +8100,9 @@
       <c r="D7" s="35" t="n"/>
       <c r="E7" s="35" t="n"/>
       <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n"/>
+      <c r="G7" s="35" t="n">
+        <v>0</v>
+      </c>
       <c r="H7" s="35" t="n">
         <v>0</v>
       </c>
@@ -7860,15 +8129,17 @@
         </is>
       </c>
       <c r="D8" s="38" t="n"/>
-      <c r="E8" s="38" t="n"/>
+      <c r="E8" s="38" t="n">
+        <v>-91118</v>
+      </c>
       <c r="F8" s="38" t="n">
-        <v>-91118</v>
+        <v>-93014</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>-93014</v>
+        <v>-104</v>
       </c>
       <c r="H8" s="38" t="n">
-        <v>-104</v>
+        <v>-99886</v>
       </c>
       <c r="I8" s="39" t="inlineStr">
         <is>
